--- a/央企红利-国企红利-港股通央企红利-消费红利_年收益率_夏普比率.xlsx
+++ b/央企红利-国企红利-港股通央企红利-消费红利_年收益率_夏普比率.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555" tabRatio="943" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="20752" windowHeight="9555" tabRatio="943" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="央企红利" sheetId="1" r:id="rId1"/>
@@ -710,7 +710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -720,17 +720,14 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1269,7 +1266,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.9557522123894" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.0796460176991" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.4336283185841" style="1" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="1" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="1" customWidth="1"/>
@@ -1303,298 +1300,318 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="1">
         <v>2009</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="E2" s="3">
+        <v>1.1079</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.3638</v>
+      </c>
       <c r="G2" s="4">
         <v>0.03</v>
       </c>
-      <c r="H2" s="2" t="e">
-        <f t="shared" ref="H2:H18" si="0">(E2-G2)/F2</f>
-        <v>#DIV/0!</v>
+      <c r="H2" s="2">
+        <f>(E2-G2)/F2</f>
+        <v>2.96289169873557</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
       <c r="D3" s="1">
         <v>2010</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="3">
+        <v>0.0432</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.2435</v>
+      </c>
       <c r="G3" s="4">
         <v>0.03</v>
       </c>
-      <c r="H3" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H3" s="2">
+        <f t="shared" ref="H2:H18" si="0">(E3-G3)/F3</f>
+        <v>0.0542094455852156</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
       <c r="D4" s="1">
         <v>2011</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="3">
+        <v>-0.2143</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.1739</v>
+      </c>
       <c r="G4" s="4">
         <v>0.03</v>
       </c>
-      <c r="H4" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.40483036227717</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
       <c r="D5" s="1">
         <v>2012</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="3">
+        <v>0.0593</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.1787</v>
+      </c>
       <c r="G5" s="4">
         <v>0.03</v>
       </c>
-      <c r="H5" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.163961947397874</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
       <c r="D6" s="1">
         <v>2013</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="3">
+        <v>-0.0898</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.1877</v>
+      </c>
       <c r="G6" s="4">
         <v>0.03</v>
       </c>
-      <c r="H6" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H6" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.63825253063399</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
       <c r="D7" s="1">
         <v>2014</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="3">
+        <v>0.7194</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.1877</v>
+      </c>
       <c r="G7" s="4">
         <v>0.03</v>
       </c>
-      <c r="H7" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>3.67288225892381</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
       <c r="D8" s="1">
         <v>2015</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="E8" s="3">
+        <v>-0.045</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.408</v>
+      </c>
       <c r="G8" s="4">
         <v>0.03</v>
       </c>
-      <c r="H8" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.183823529411765</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
       <c r="D9" s="1">
         <v>2016</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="3">
+        <v>-0.0817</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.1844</v>
+      </c>
       <c r="G9" s="4">
         <v>0.03</v>
       </c>
-      <c r="H9" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.605748373101952</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
       <c r="D10" s="1">
         <v>2017</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="3">
+        <v>0.1543</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.0858</v>
+      </c>
       <c r="G10" s="4">
         <v>0.03</v>
       </c>
-      <c r="H10" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
+        <v>1.44871794871795</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
       <c r="D11" s="1">
         <v>2018</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="3">
+        <v>-0.1253</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.1868</v>
+      </c>
       <c r="G11" s="4">
         <v>0.03</v>
       </c>
-      <c r="H11" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H11" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.831370449678801</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
       <c r="D12" s="1">
         <v>2019</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="3">
+        <v>0.0751</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.168</v>
+      </c>
       <c r="G12" s="4">
         <v>0.03</v>
       </c>
-      <c r="H12" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.268452380952381</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
       <c r="D13" s="1">
         <v>2020</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="E13" s="3">
+        <v>-0.0789</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.1882</v>
+      </c>
       <c r="G13" s="4">
         <v>0.03</v>
       </c>
-      <c r="H13" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H13" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.578639744952179</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
       <c r="D14" s="1">
         <v>2021</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="3">
+        <v>0.0971</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.195</v>
+      </c>
       <c r="G14" s="4">
         <v>0.03</v>
       </c>
-      <c r="H14" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.344102564102564</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
       <c r="D15" s="1">
         <v>2022</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="E15" s="3">
+        <v>-0.0627</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.1824</v>
+      </c>
       <c r="G15" s="4">
         <v>0.03</v>
       </c>
-      <c r="H15" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H15" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.508223684210526</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
       <c r="D16" s="1">
         <v>2023</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="E16" s="3">
+        <v>0.0278</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.1418</v>
+      </c>
       <c r="G16" s="4">
         <v>0.03</v>
       </c>
-      <c r="H16" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="H16" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.0155148095909732</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8">
       <c r="D17" s="1">
         <v>2024</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="E17" s="3">
+        <v>0.231</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.1869</v>
+      </c>
       <c r="G17" s="4">
         <v>0.03</v>
       </c>
-      <c r="H17" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="H17" s="2">
+        <f t="shared" si="0"/>
+        <v>1.07544141252006</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8">
       <c r="D18" s="1">
         <v>2025</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="E18" s="3">
+        <v>0.0568</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.1198</v>
+      </c>
       <c r="G18" s="4">
         <v>0.03</v>
       </c>
-      <c r="H18" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.223706176961603</v>
       </c>
     </row>
   </sheetData>
@@ -1611,11 +1628,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.0796460176991" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.4336283185841" style="1" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="1" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="1" customWidth="1"/>
@@ -1648,353 +1665,389 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="1" spans="1:8">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E2" s="3">
+        <v>-0.4693</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.2429</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H2" s="2">
+        <f>(E2-G2)/F2</f>
+        <v>-2.05557842733635</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:8">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1">
+        <v>2007</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.9641</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.4254</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H21" si="0">(E3-G3)/F3</f>
+        <v>4.54654442877292</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1">
+        <v>2008</v>
+      </c>
+      <c r="E4" s="3">
+        <v>-0.6253</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.4849</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.35141266240462</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:8">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1">
+        <v>2009</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.0308</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.3459</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="0"/>
+        <v>2.89332176929748</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="D6" s="1">
         <v>2010</v>
       </c>
-      <c r="E2" s="5">
-        <v>-0.0611</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0.2198</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H2" s="2">
-        <f t="shared" ref="H2:H17" si="0">(E2-G2)/F2</f>
-        <v>-0.414467697907188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="1">
+      <c r="E6" s="3">
+        <v>-0.0309</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.2334</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.260925449871465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="D7" s="1">
         <v>2011</v>
       </c>
-      <c r="E3" s="5">
-        <v>-0.1854</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.1725</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H3" s="2">
-        <f t="shared" si="0"/>
-        <v>-1.24869565217391</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="1">
+      <c r="E7" s="3">
+        <v>-0.2563</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.1834</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.56106870229008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="D8" s="1">
         <v>2012</v>
       </c>
-      <c r="E4" s="5">
-        <v>0.0311</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0.1651</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" si="0"/>
-        <v>0.00666262870987281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="1">
+      <c r="E8" s="3">
+        <v>0.052</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1898</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.1159114857745</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="D9" s="1">
         <v>2013</v>
       </c>
-      <c r="E5" s="5">
-        <v>0.0377</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.1808</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.0425884955752212</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="1">
+      <c r="E9" s="3">
+        <v>-0.0177</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.183</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.260655737704918</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="D10" s="1">
         <v>2014</v>
       </c>
-      <c r="E6" s="5">
-        <v>0.6661</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.1794</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H6" s="2">
-        <f t="shared" si="0"/>
-        <v>3.54570791527313</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="1">
+      <c r="E10" s="3">
+        <v>0.599</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.1828</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
+        <v>3.11269146608315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="D11" s="1">
         <v>2015</v>
       </c>
-      <c r="E7" s="5">
-        <v>0.2597</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.4025</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="0"/>
-        <v>0.570683229813664</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="1">
+      <c r="E11" s="3">
+        <v>0.058</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.4152</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0674373795761079</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="D12" s="1">
         <v>2016</v>
       </c>
-      <c r="E8" s="5">
-        <v>-0.0142</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0.2006</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.220338983050847</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="1">
+      <c r="E12" s="3">
+        <v>-0.0593</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.1885</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.473740053050398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="D13" s="1">
         <v>2017</v>
       </c>
-      <c r="E9" s="5">
-        <v>0.1203</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0.0751</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="0"/>
-        <v>1.20239680426099</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="1">
+      <c r="E13" s="3">
+        <v>0.2304</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.093</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="0"/>
+        <v>2.15483870967742</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="D14" s="1">
         <v>2018</v>
       </c>
-      <c r="E10" s="5">
-        <v>-0.1699</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0.1711</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="0"/>
-        <v>-1.16832261835184</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="1">
+      <c r="E14" s="3">
+        <v>-0.1708</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.1875</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.07093333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="D15" s="1">
         <v>2019</v>
       </c>
-      <c r="E11" s="5">
-        <v>0.1243</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.161</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="0"/>
-        <v>0.585714285714286</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="1">
+      <c r="E15" s="3">
+        <v>0.1723</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.1761</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.808063600227144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="D16" s="1">
         <v>2020</v>
       </c>
-      <c r="E12" s="5">
-        <v>-0.0198</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0.1889</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.26363155108523</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="1">
+      <c r="E16" s="3">
+        <v>-0.0268</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.206</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.275728155339806</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8">
+      <c r="D17" s="1">
         <v>2021</v>
       </c>
-      <c r="E13" s="5">
-        <v>0.139</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.1337</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H13" s="2">
-        <f t="shared" si="0"/>
-        <v>0.81525804038893</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="1">
+      <c r="E17" s="3">
+        <v>0.1078</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.1811</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.429596907785754</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8">
+      <c r="D18" s="1">
         <v>2022</v>
       </c>
-      <c r="E14" s="5">
-        <v>-0.0392</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0.1729</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H14" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.400231347599769</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="1">
+      <c r="E18" s="3">
+        <v>-0.0082</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.2015</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.189578163771712</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8">
+      <c r="D19" s="1">
         <v>2023</v>
       </c>
-      <c r="E15" s="5">
-        <v>0.0874</v>
-      </c>
-      <c r="F15" s="5">
-        <v>0.1134</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H15" s="2">
-        <f t="shared" si="0"/>
-        <v>0.506172839506173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="1">
+      <c r="E19" s="3">
+        <v>0.0317</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.1251</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0135891286970424</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8">
+      <c r="D20" s="1">
         <v>2024</v>
       </c>
-      <c r="E16" s="5">
-        <v>0.127</v>
-      </c>
-      <c r="F16" s="5">
-        <v>0.1891</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H16" s="2">
-        <f t="shared" si="0"/>
-        <v>0.512956107879429</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="1">
+      <c r="E20" s="3">
+        <v>0.1384</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.1973</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.549417131272174</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8">
+      <c r="D21" s="1">
         <v>2025</v>
       </c>
-      <c r="E17" s="5">
-        <v>-0.0071</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0.1131</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0.03</v>
-      </c>
-      <c r="H17" s="2">
-        <f t="shared" si="0"/>
-        <v>-0.328028293545535</v>
+      <c r="E21" s="3">
+        <v>-0.0045</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.123</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.280487804878049</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A17"/>
-    <mergeCell ref="B2:B17"/>
-    <mergeCell ref="C2:C17"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="C2:C21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2008,8 +2061,8 @@
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.283185840708" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4336283185841" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.2743362831858" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6283185840708" style="1" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="1" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.4336283185841" style="2" customWidth="1"/>
@@ -2042,196 +2095,210 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>931233</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="1">
         <v>2015</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="E2" s="3">
+        <v>-0.116</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.2993</v>
+      </c>
       <c r="G2" s="4">
         <v>0.03</v>
       </c>
-      <c r="H2" s="2" t="e">
+      <c r="H2" s="2">
         <f t="shared" ref="H2:H12" si="0">(E2-G2)/F2</f>
-        <v>#DIV/0!</v>
+        <v>-0.48780487804878</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
       <c r="D3" s="1">
         <v>2016</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="E3" s="3">
+        <v>-0.0398</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.2186</v>
+      </c>
       <c r="G3" s="4">
         <v>0.03</v>
       </c>
-      <c r="H3" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H3" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.319304666056725</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
       <c r="D4" s="1">
         <v>2017</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="3">
+        <v>0.1632</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.1265</v>
+      </c>
       <c r="G4" s="4">
         <v>0.03</v>
       </c>
-      <c r="H4" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>1.05296442687747</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
       <c r="D5" s="1">
         <v>2018</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="E5" s="3">
+        <v>-0.0879</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.204</v>
+      </c>
       <c r="G5" s="4">
         <v>0.03</v>
       </c>
-      <c r="H5" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H5" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.577941176470588</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
       <c r="D6" s="1">
         <v>2019</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="3">
+        <v>-0.0069</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.1489</v>
+      </c>
       <c r="G6" s="4">
         <v>0.03</v>
       </c>
-      <c r="H6" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H6" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.247817327065144</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
       <c r="D7" s="1">
         <v>2020</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="3">
+        <v>-0.212</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.2459</v>
+      </c>
       <c r="G7" s="4">
         <v>0.03</v>
       </c>
-      <c r="H7" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.984139894265962</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
       <c r="D8" s="1">
         <v>2021</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="E8" s="3">
+        <v>0.1772</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.1818</v>
+      </c>
       <c r="G8" s="4">
         <v>0.03</v>
       </c>
-      <c r="H8" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.80968096809681</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
       <c r="D9" s="1">
         <v>2022</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="E9" s="3">
+        <v>-0.1071</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.2326</v>
+      </c>
       <c r="G9" s="4">
         <v>0.03</v>
       </c>
-      <c r="H9" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.589423903697334</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
       <c r="D10" s="1">
         <v>2023</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="3">
+        <v>-0.0202</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.1801</v>
+      </c>
       <c r="G10" s="4">
         <v>0.03</v>
       </c>
-      <c r="H10" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.278734036646308</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
       <c r="D11" s="1">
         <v>2024</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="3">
+        <v>0.3089</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.3056</v>
+      </c>
       <c r="G11" s="4">
         <v>0.03</v>
       </c>
-      <c r="H11" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.912630890052356</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
       <c r="D12" s="1">
         <v>2025</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="3">
+        <v>0.1799</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.1839</v>
+      </c>
       <c r="G12" s="4">
         <v>0.03</v>
       </c>
-      <c r="H12" s="2" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+      <c r="H12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.815116911364872</v>
       </c>
     </row>
   </sheetData>
@@ -2252,7 +2319,7 @@
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.283185840708" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.0796460176991" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.4336283185841" style="1" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="1" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="1" customWidth="1"/>
@@ -2286,277 +2353,393 @@
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="1">
         <v>2006</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="E2" s="3">
+        <v>1.76</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.2447</v>
+      </c>
       <c r="G2" s="4">
         <v>0.03</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2">
+        <f>(E2-G2)/F2</f>
+        <v>7.06988148753576</v>
+      </c>
     </row>
     <row r="3" customFormat="1" spans="1:8">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>2007</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="E3" s="3">
+        <v>1.8195</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.3972</v>
+      </c>
       <c r="G3" s="4">
         <v>0.03</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H21" si="0">(E3-G3)/F3</f>
+        <v>4.50528700906344</v>
+      </c>
     </row>
     <row r="4" customFormat="1" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>2008</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="E4" s="3">
+        <v>-0.4622</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.5738</v>
+      </c>
       <c r="G4" s="4">
         <v>0.03</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.857790170791216</v>
+      </c>
     </row>
     <row r="5" customFormat="1" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>2009</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="E5" s="3">
+        <v>1.2322</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.3351</v>
+      </c>
       <c r="G5" s="4">
         <v>0.03</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2">
+        <f t="shared" si="0"/>
+        <v>3.58758579528499</v>
+      </c>
     </row>
     <row r="6" customFormat="1" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
       <c r="D6" s="1">
         <v>2010</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="E6" s="3">
+        <v>0.2837</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.2647</v>
+      </c>
       <c r="G6" s="4">
         <v>0.03</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.958443520967133</v>
+      </c>
     </row>
     <row r="7" customFormat="1" spans="1:8">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
       <c r="D7" s="1">
         <v>2011</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="E7" s="3">
+        <v>-0.2286</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.191</v>
+      </c>
       <c r="G7" s="4">
         <v>0.03</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.35392670157068</v>
+      </c>
     </row>
     <row r="8" customFormat="1" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>2012</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="E8" s="3">
+        <v>-0.007</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.2381</v>
+      </c>
       <c r="G8" s="4">
         <v>0.03</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.155396892062159</v>
+      </c>
     </row>
     <row r="9" customFormat="1" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>2013</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="3">
+        <v>0.0482</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.2212</v>
+      </c>
       <c r="G9" s="4">
         <v>0.03</v>
       </c>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.0822784810126582</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
       <c r="D10" s="1">
         <v>2014</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="3">
+        <v>0.3407</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.189</v>
+      </c>
       <c r="G10" s="4">
         <v>0.03</v>
       </c>
+      <c r="H10" s="2">
+        <f t="shared" si="0"/>
+        <v>1.64391534391534</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
       <c r="D11" s="1">
         <v>2015</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="E11" s="3">
+        <v>0.2882</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.4269</v>
+      </c>
       <c r="G11" s="4">
         <v>0.03</v>
       </c>
+      <c r="H11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.60482548606231</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
       <c r="D12" s="1">
         <v>2016</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="3">
+        <v>0.0668</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.2399</v>
+      </c>
       <c r="G12" s="4">
         <v>0.03</v>
       </c>
+      <c r="H12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.153397248853689</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
       <c r="D13" s="1">
         <v>2017</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="E13" s="3">
+        <v>0.3211</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.1536</v>
+      </c>
       <c r="G13" s="4">
         <v>0.03</v>
       </c>
+      <c r="H13" s="2">
+        <f t="shared" si="0"/>
+        <v>1.89518229166667</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
       <c r="D14" s="1">
         <v>2018</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="3">
+        <v>-0.1376</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.2492</v>
+      </c>
       <c r="G14" s="4">
         <v>0.03</v>
       </c>
+      <c r="H14" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.672552166934189</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
       <c r="D15" s="1">
         <v>2019</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="E15" s="3">
+        <v>0.5381</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.2243</v>
+      </c>
       <c r="G15" s="4">
         <v>0.03</v>
       </c>
+      <c r="H15" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2652697280428</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
       <c r="D16" s="1">
         <v>2020</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="E16" s="3">
+        <v>0.4617</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.275</v>
+      </c>
       <c r="G16" s="4">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="H16" s="2">
+        <f t="shared" si="0"/>
+        <v>1.56981818181818</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8">
       <c r="D17" s="1">
         <v>2021</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="E17" s="3">
+        <v>0.1112</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.212</v>
+      </c>
       <c r="G17" s="4">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="H17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.383018867924528</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8">
       <c r="D18" s="1">
         <v>2022</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="E18" s="3">
+        <v>-0.0927</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0.2385</v>
+      </c>
       <c r="G18" s="4">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="H18" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.514465408805031</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8">
       <c r="D19" s="1">
         <v>2023</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="E19" s="3">
+        <v>-0.1562</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.1396</v>
+      </c>
       <c r="G19" s="4">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="H19" s="2">
+        <f t="shared" si="0"/>
+        <v>-1.33381088825215</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8">
       <c r="D20" s="1">
         <v>2024</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="E20" s="3">
+        <v>-0.0511</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.2588</v>
+      </c>
       <c r="G20" s="4">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+      <c r="H20" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.313369397217929</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8">
       <c r="D21" s="1">
         <v>2025</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="E21" s="3">
+        <v>0.0125</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.1608</v>
+      </c>
       <c r="G21" s="4">
         <v>0.03</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="0"/>
+        <v>-0.108830845771144</v>
       </c>
     </row>
   </sheetData>
